--- a/MassiveShalom.xlsx
+++ b/MassiveShalom.xlsx
@@ -1,124 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\MassiveSHALOM JD\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62023A00-BD6C-47E8-AA71-A539E9AC057B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t>CODIGO</t>
-  </si>
-  <si>
-    <t>CLIENTE</t>
-  </si>
-  <si>
-    <t>DNI</t>
-  </si>
-  <si>
-    <t>CELULAR</t>
-  </si>
-  <si>
-    <t>AGENCIA SHALOM</t>
-  </si>
-  <si>
-    <t>UNION DE PRODUCTOS</t>
-  </si>
-  <si>
-    <t>MONTO TOTAL</t>
-  </si>
-  <si>
-    <t>AGENCIA</t>
-  </si>
-  <si>
-    <t>DÍA PROGRAMADO ENTREGA</t>
-  </si>
-  <si>
-    <t>¿SE ENVIO?</t>
-  </si>
-  <si>
-    <t>CLAVE</t>
-  </si>
-  <si>
-    <t>ESTADO</t>
-  </si>
-  <si>
-    <t>#NVD70697</t>
-  </si>
-  <si>
-    <t>SANDRA MILAGROS CORDOVA MELENDEZ</t>
-  </si>
-  <si>
-    <t>RIOJA</t>
-  </si>
-  <si>
-    <t>1 KIT DE 12 BOLIGRAFOS PARA UÑAS + 1 PRODUCTO REGALO MUJER + 1 CUBRE CANAS EN BARRA NEGRO</t>
-  </si>
-  <si>
-    <t>S/.128,00</t>
-  </si>
-  <si>
-    <t>PENDIENTE</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -139,6 +75,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000FF00"/>
+        <bgColor rgb="0000FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -199,45 +141,105 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -503,99 +505,143 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="58.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col width="10.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="25.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="9" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="19.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="58.7109375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="16.140625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="10" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="31.140625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="12" bestFit="1" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
+    <row r="1" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CODIGO</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>CLIENTE</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>CELULAR</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>AGENCIA SHALOM</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>UNION DE PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>MONTO TOTAL</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>AGENCIA</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>DÍA PROGRAMADO ENTREGA</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>¿SE ENVIO?</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>CLAVE</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ESTADO</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="7">
+    <row r="2" ht="27" customHeight="1" thickBot="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>#NVD70697</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>SANDRA MILAGROS CORDOVA MELENDEZ</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
         <v>70478462</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="7" t="n">
         <v>969639069</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="8">
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>1 KIT DE 12 BOLIGRAFOS PARA UÑAS + 1 PRODUCTO REGALO MUJER + 1 CUBRE CANAS EN BARRA NEGRO</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>S/.128,00</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="8" t="n">
         <v>46079</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="4">
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="n">
         <v>6060</v>
       </c>
-      <c r="L2" s="9"/>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDIO</t>
+        </is>
+      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C7" s="5"/>
+    <row r="7">
+      <c r="C7" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
--- a/MassiveShalom.xlsx
+++ b/MassiveShalom.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,16 +43,8 @@
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -73,14 +65,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000FF00"/>
-        <bgColor rgb="0000FF00"/>
+        <fgColor rgb="FFFFA500"/>
+        <bgColor rgb="FFFFA500"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFA500"/>
+        <bgColor rgb="FFFFA500"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFA500"/>
+        <bgColor rgb="00FFA500"/>
       </patternFill>
     </fill>
   </fills>
@@ -141,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -152,21 +162,28 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -510,12 +527,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="10.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="25.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="9" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="9.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="10.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="19.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
     <col width="58.7109375" bestFit="1" customWidth="1" min="6" max="6"/>
@@ -588,57 +605,504 @@
       </c>
     </row>
     <row r="2" ht="27" customHeight="1" thickBot="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>#NVD70697</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>SANDRA MILAGROS CORDOVA MELENDEZ</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="n">
-        <v>70478462</v>
-      </c>
-      <c r="D2" s="7" t="n">
-        <v>969639069</v>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>1 KIT DE 12 BOLIGRAFOS PARA UÑAS + 1 PRODUCTO REGALO MUJER + 1 CUBRE CANAS EN BARRA NEGRO</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>S/.128,00</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="8" t="n">
-        <v>46079</v>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>6060</v>
-      </c>
-      <c r="L2" s="10" t="inlineStr">
-        <is>
-          <t>PROCEDIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="C7" s="5" t="n"/>
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#NVD73068</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>JUAN ALEX VISCAINO VASQUEZ</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>47947473</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>908931133</v>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>PUENTE VIRU</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>1 CANGURERA DE CUERO PU PARA HOMBRE + 1 PRODUCTO REGALO HOMBRE</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>S/.139,00</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>SHALOM</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="n">
+        <v>46092</v>
+      </c>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" t="n">
+        <v>2050</v>
+      </c>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>NO PROCEDIO POR ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>#NVD73073</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>WILIAN OSWALDO SANTISTEBAN ASCOY</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>18906351</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>990707508</v>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>PAIJAN</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>2 ADAPTADOR DE TALADRO + 1 PRODUCTO REGALO HOMBRE</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>S/.129,00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>SHALOM</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>46092</v>
+      </c>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" t="n">
+        <v>9060</v>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>NO PROCEDIO POR ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1" thickBot="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>#NVD73036</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>JOSE CARLOS APAZA ALEMAN</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1235177</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>970023073</v>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>AV COSTANERA</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1 SOPORTE 360 CON PARLANTE DE INDUCCION Y TRIPODE + 1 PRODUCTO REGALO HOMBRE</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>S/.129,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>SHALOM</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>46092</v>
+      </c>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" t="n">
+        <v>6556</v>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>NO PROCEDIO POR ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1" thickBot="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>#NVD73032</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>LESLY YOSSELYN GAMBOA YUCRA</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>70994910</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>960185692</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>MALA</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>3 STRAPLESS PUSH-UP BRA - TALLA C + 1 PRODUCTO REGALO MUJER</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>S/.99,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>SHALOM</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>46092</v>
+      </c>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" t="n">
+        <v>3212</v>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>NO PROCEDIO POR ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1" thickBot="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>#NVD73010</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>WAIMER ROLANDO PAREDES NARVAEZ</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>45683827</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>934912774</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>AV JOSE GALVEZ</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1 CANGURERA DE CUERO PU PARA HOMBRE + 1 PRODUCTO REGALO HOMBRE</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>S/.139,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>SHALOM</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>46092</v>
+      </c>
+      <c r="J6" s="4" t="n"/>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>NO PROCEDIO POR ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1" thickBot="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="L7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="39.75" customHeight="1" thickBot="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="L8" s="8" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="L9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1" thickBot="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="L10" s="8" t="n"/>
+    </row>
+    <row r="11" ht="27" customHeight="1" thickBot="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="L11" s="8" t="n"/>
+    </row>
+    <row r="12" ht="27" customHeight="1" thickBot="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="L12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1" thickBot="1">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="L13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="L14" s="8" t="n"/>
+    </row>
+    <row r="15" ht="39.75" customHeight="1" thickBot="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="L15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="27" customHeight="1" thickBot="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="L16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="27" customHeight="1" thickBot="1">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="L17" s="8" t="n"/>
+    </row>
+    <row r="18" ht="27" customHeight="1" thickBot="1">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="L18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="27" customHeight="1" thickBot="1">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="L19" s="8" t="n"/>
+    </row>
+    <row r="20" ht="27" customHeight="1" thickBot="1">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="L20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="27" customHeight="1" thickBot="1">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="L21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="52.5" customHeight="1" thickBot="1">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="L22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="27" customHeight="1" thickBot="1">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="L23" s="8" t="n"/>
+    </row>
+    <row r="24" ht="27" customHeight="1" thickBot="1">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="L24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="27" customHeight="1" thickBot="1">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="L25" s="8" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" thickBot="1">
+      <c r="J26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" thickBot="1">
+      <c r="J27" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
